--- a/Coupang_Top20_20260623.xlsx
+++ b/Coupang_Top20_20260623.xlsx
@@ -448,280 +448,280 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>홈플래닛 베이직 스탠드 선풍기</t>
+          <t>아이리버 25W 2포트 초고속 가정용 충전기 + CtoC 케이블 세트</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25190</v>
+        <v>8800</v>
       </c>
       <c r="C2">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=7212367661&amp;itemId=18255669809&amp;vendorItemId=85402293544&amp;traceid=V0-113-7d78e232e50964e0", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8939019740&amp;itemId=26138373322&amp;vendorItemId=93118512226&amp;traceid=V0-113-fd1e07a2d9481cd8", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>브리타 정수기 필터 막스트라 프로 퓨어 퍼포먼스 3입</t>
+          <t>홈플래닛 25W PPS PD 3.0 초고속 충전기 + CtoC 케이블 1.2m</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21850</v>
+        <v>7290</v>
       </c>
       <c r="C3">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=9102889885&amp;itemId=23756832465&amp;vendorItemId=90781295338&amp;traceid=V0-113-59ae32451442015d", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=5047898639&amp;itemId=6804859657&amp;vendorItemId=74097543659&amp;traceid=V0-113-482c6187a1b37f79", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>알리사 100단 아이스 터보 MAX 휴대용 선풍기</t>
+          <t>홈플래닛 핸디형 스탠드 스팀다리미</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24980</v>
+        <v>28990</v>
       </c>
       <c r="C4">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8719219704&amp;itemId=25325956860&amp;vendorItemId=92859054401&amp;traceid=V0-113-3390c08a48f3cae9", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=310080038&amp;itemId=977484067&amp;vendorItemId=5392665218&amp;traceid=V0-113-c73a6d2a7fbf4b52", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>홈플래닛 발터치 리모컨 스탠드형 선풍기</t>
+          <t>필립스 무선 ENC노이즈캔슬링 블루투스 이어폰</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>33890</v>
+        <v>18900</v>
       </c>
       <c r="C5">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=1459643219&amp;itemId=2511597502&amp;vendorItemId=92134731921&amp;traceid=V0-113-62386184a6cb7f37", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8498887873&amp;itemId=24600675528&amp;vendorItemId=91612183770&amp;traceid=V0-113-53ee2dd24dc6f077", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>신지모루 오피디 25W GaN 듀얼포트 PPS 초고속 PD 충전기</t>
+          <t>Apple 정품 20W USB-C 전원 어댑터 MUW13KH/A</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8980</v>
+        <v>20800</v>
       </c>
       <c r="C6">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=7415163807&amp;itemId=19222022188&amp;vendorItemId=86338760049&amp;traceid=V0-113-693c11efc2bbce39", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=2270230024&amp;itemId=22170383583&amp;vendorItemId=88946948908&amp;traceid=V0-113-fad4b0f7464d90db", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>앳플리 디지털 LED 체중계</t>
+          <t>팬톤 PD 22.5W 초고속충전 대용량 케이블 일체형 미러 보조배터리 10000mAh PGB-20</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13900</v>
+        <v>17900</v>
       </c>
       <c r="C7">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=6417202386&amp;itemId=13788880930&amp;vendorItemId=81039306234&amp;traceid=V0-113-6b4b0425db2ef1f6", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=7925483056&amp;itemId=21787007370&amp;vendorItemId=88835705792&amp;traceid=V0-113-f89728f61fd6871b", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>홈플래닛 25W PPS PD 3.0 초고속 충전기 + CtoC 케이블 1.2m</t>
+          <t>액센 프리미엄 캐릭터 마이크로 SD카드</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7290</v>
+        <v>19800</v>
       </c>
       <c r="C8">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=5047898639&amp;itemId=6804859657&amp;vendorItemId=74097543659&amp;traceid=V0-113-482c6187a1b37f79", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=7704604385&amp;itemId=6156844140&amp;vendorItemId=73453040955&amp;traceid=V0-113-a6ffe7d8068452b2", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>로지텍 무소음 무선 마우스</t>
+          <t>[삼성 감사 페스티벌] 삼성전자 갤럭시 버즈3 FE 블루투스 이어폰</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25100</v>
+        <v>133720</v>
       </c>
       <c r="C9">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=6159950381&amp;itemId=11948008563&amp;vendorItemId=3299873959&amp;traceid=V0-113-a5be5e5f7b0a2d69", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=9019055318&amp;itemId=26442741419&amp;vendorItemId=93418323317&amp;traceid=V0-113-1ffb8e6cf2c2ae7c", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>홈플래닛 핸디형 스탠드 스팀다리미</t>
+          <t>신지모루 로프 C타입 고속충전 케이블</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>28990</v>
+        <v>8900</v>
       </c>
       <c r="C10">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=310080038&amp;itemId=977484067&amp;vendorItemId=5392665218&amp;traceid=V0-113-c73a6d2a7fbf4b52", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=7900401137&amp;itemId=926533007&amp;vendorItemId=5302365610&amp;traceid=V0-113-c1147fc604802442", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>필립스 무선 ENC노이즈캔슬링 블루투스 이어폰</t>
+          <t>[삼성 감사 페스티벌] 삼성전자 인버터 제습기 18L</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18900</v>
+        <v>402920</v>
       </c>
       <c r="C11">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8498887873&amp;itemId=24600675528&amp;vendorItemId=91612183770&amp;traceid=V0-113-53ee2dd24dc6f077", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=9398164042&amp;itemId=27913834829&amp;vendorItemId=94872476374&amp;traceid=V0-113-5027b1a8b1e8ff2d", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>액센 프리미엄 캐릭터 마이크로 SD카드</t>
+          <t>에버튼하우스 에그쿠커</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19800</v>
+        <v>8500</v>
       </c>
       <c r="C12">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=7704604385&amp;itemId=6156844140&amp;vendorItemId=73453040955&amp;traceid=V0-113-a6ffe7d8068452b2", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=283693738&amp;itemId=18656743421&amp;vendorItemId=70683242414&amp;traceid=V0-113-c77feddeeb9a1c86", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>팬톤 PD 22.5W 초고속충전 대용량 케이블 일체형 미러 보조배터리 10000mAh PGB-20</t>
+          <t>루메나 무선 탁상용선풍기</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17900</v>
+        <v>35910</v>
       </c>
       <c r="C13">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=7925483056&amp;itemId=21787007370&amp;vendorItemId=88835705792&amp;traceid=V0-113-f89728f61fd6871b", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=9041217547&amp;itemId=22524207601&amp;vendorItemId=89545588602&amp;traceid=V0-113-93af8ab0ce6bd264", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>에버튼하우스 에그쿠커</t>
+          <t>카스토리 벽걸이 에어컨 윈드바이저 바람막이 가림막 무타공 걸이형 길이조절</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8500</v>
+        <v>5680</v>
       </c>
       <c r="C14">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=283693738&amp;itemId=18656743421&amp;vendorItemId=70683242414&amp;traceid=V0-113-c77feddeeb9a1c86", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=9544352055&amp;itemId=17793481362&amp;vendorItemId=95473605448&amp;traceid=V0-113-45ed21b6e37ef741", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>루메나 무선 탁상용선풍기</t>
+          <t>아이리버 3.5mm AUX 갤럭시 노트북 컴퓨터 알루미늄 커널형 유선 이어폰, BHC-70M, 블랙</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>37300</v>
+        <v>7900</v>
       </c>
       <c r="C15">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=9041217547&amp;itemId=22524207601&amp;vendorItemId=89545588602&amp;traceid=V0-113-93af8ab0ce6bd264", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8602654934&amp;itemId=24944896878&amp;vendorItemId=91980127301&amp;traceid=V0-113-cef1a24c3259468a", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>유닉스 세라믹 판고데기</t>
+          <t>에이케이리빙 유파 발터치 리모컨 선풍기</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>24900</v>
+        <v>35800</v>
       </c>
       <c r="C16">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8729115745&amp;itemId=25361584612&amp;vendorItemId=3089081003&amp;traceid=V0-113-c054456fc302c5b1", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8225143195&amp;itemId=23653576267&amp;vendorItemId=92283755564&amp;traceid=V0-113-ba7b61a7e8a8ec65", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>홈플래닛 디지털 LED 가정용 체중계</t>
+          <t>셀루미 메가 스틱 올인원 스마트폰 셀카봉 삼각대 171.7cm</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8990</v>
+        <v>12700</v>
       </c>
       <c r="C17">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8359676766&amp;itemId=24158126424&amp;vendorItemId=91176755808&amp;traceid=V0-113-bd08c10e4eabdcc5", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8915242678&amp;itemId=26046876968&amp;vendorItemId=93028357799&amp;traceid=V0-113-32aa3336abf6cce1", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>아이리버 3.5mm AUX 갤럭시 노트북 컴퓨터 알루미늄 커널형 유선 이어폰, BHC-70M, 블랙</t>
+          <t>디에스가추몰 충전식 무선 멀티 핸디 청소기 강력 흡입 초경량 진공청소기</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7900</v>
+        <v>19140</v>
       </c>
       <c r="C18">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8602654934&amp;itemId=24944896878&amp;vendorItemId=91980127301&amp;traceid=V0-113-cef1a24c3259468a", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=9427713974&amp;itemId=28026946675&amp;vendorItemId=95508572856&amp;traceid=V0-113-9f4d45253e4894f3", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>에이케이리빙 유파 발터치 리모컨 선풍기</t>
+          <t>애플 Lightning USB C 1m 케이블</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>35800</v>
+        <v>20000</v>
       </c>
       <c r="C19">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8225143195&amp;itemId=23653576267&amp;vendorItemId=92283755564&amp;traceid=V0-113-ba7b61a7e8a8ec65", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=6135671310&amp;itemId=26739810964&amp;vendorItemId=88946948877&amp;traceid=V0-113-263cad63aa6054db", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SUNGOD 헤어 드라이기 블루라이트 케어 고출력 파워풍량 2000W 저소음 가정용 휴대용</t>
+          <t>프라임큐 C타입 오픈형 유선 이어폰</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>24800</v>
+        <v>5830</v>
       </c>
       <c r="C20">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8999614825&amp;itemId=26372111897&amp;vendorItemId=95143920498&amp;traceid=V0-113-f2db7f312cdbdad8", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=7842640108&amp;itemId=21353802010&amp;vendorItemId=81754468157&amp;traceid=V0-113-d555f442edff9f15", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>애플 Lightning USB C 1m 케이블</t>
+          <t>홈플래닛 퀄컴 공식인증 QC3.0 18W고속충전기 + 타입C케이블 1.2m 세트</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>20000</v>
+        <v>7490</v>
       </c>
       <c r="C21">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=6135671310&amp;itemId=26739810964&amp;vendorItemId=88946948877&amp;traceid=V0-113-263cad63aa6054db", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=1628630781&amp;itemId=2778296479&amp;vendorItemId=89645323681&amp;traceid=V0-113-e16801aaf71b1d25", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
